--- a/DateBase/orders/Nha Thu_2026-6-11.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-11.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510557101016753052020151515150</v>
+        <v>05510557101016753052020151515155</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-11.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,95 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>415_百子莲_Agapanthus_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>6</v>
+      </c>
+      <c r="C31" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510557101016753052020151515155</v>
+        <v>05510557101016753052020151515155100505030100100201530</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-11.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -692,10 +692,99 @@
       <c r="C31" t="str">
         <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>7</v>
+      </c>
+      <c r="C32" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>1</v>
+      </c>
+      <c r="C33" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>302_彩星 浅粉_Tinted Gypso light pink_undefined_0.5kg</v>
+      </c>
+      <c r="F35" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2</v>
+      </c>
+      <c r="C37" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>302_彩星 浅粉_Tinted Gypso light pink_undefined_0.5kg</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -750,7 +839,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510557101016753052020151515155100505030100100201530</v>
+        <v>05510557101016753052020151515155100505030100100201533032022111120243150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-11.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-11.xlsx
@@ -781,6 +781,9 @@
       <c r="C41" t="str">
         <v>302_彩星 浅粉_Tinted Gypso light pink_undefined_0.5kg</v>
       </c>
+      <c r="F41" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -839,7 +842,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510557101016753052020151515155100505030100100201533032022111120243150</v>
+        <v>05510557101016753052020151515155100505030100100201533032022111120243152</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-11.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -782,12 +782,72 @@
         <v>302_彩星 浅粉_Tinted Gypso light pink_undefined_0.5kg</v>
       </c>
       <c r="F41" t="str">
-        <v>2</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>427_新娘_Blushing Bride_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>3</v>
+      </c>
+      <c r="C44" t="str" xml:space="preserve">
+        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -842,7 +902,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05510557101016753052020151515155100505030100100201533032022111120243152</v>
+        <v>0551055710101675305202015151515510050503010010020153303202211112024315292015304305010</v>
       </c>
     </row>
   </sheetData>
